--- a/data/wakabasai_exhibitor.xlsx
+++ b/data/wakabasai_exhibitor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haru/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haru/Documents/webdev/wakabasai2026/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A35B0D4-B0AB-8944-B7AD-31D8AC9D06FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5A8D5C8-8FCB-A148-9681-D869712D451A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="580" windowWidth="25600" windowHeight="16060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="298">
   <si>
     <t>ロボット技術研究会</t>
   </si>
@@ -1066,12 +1066,86 @@
   <si>
     <t>https://drive.google.com/file/d/15VZBTAjMWHZ7b6BAmwfmehfksblfjNe3/view?usp=sharing</t>
   </si>
+  <si>
+    <t>circle_booth_title</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>circle_booth_location</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>circle_booth_date</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>制作物展示</t>
+  </si>
+  <si>
+    <t>VGの活動紹介</t>
+  </si>
+  <si>
+    <t>テニス部の活動紹介</t>
+  </si>
+  <si>
+    <t>„VR“でハンググライダー体験</t>
+  </si>
+  <si>
+    <t>美術部</t>
+  </si>
+  <si>
+    <t>無線研究部　技術者あつまれ〜</t>
+  </si>
+  <si>
+    <t>弓道部 説明会</t>
+  </si>
+  <si>
+    <t>フォークソングサークル(FSC)</t>
+  </si>
+  <si>
+    <t>裏千家茶道部体験会・相談会</t>
+  </si>
+  <si>
+    <t>What's jizi</t>
+  </si>
+  <si>
+    <t>オリエンって何ですか？</t>
+  </si>
+  <si>
+    <t>水泳部と話そう</t>
+  </si>
+  <si>
+    <t>クラッシックギター体験会</t>
+  </si>
+  <si>
+    <t>天文研究部 活動紹介ブース</t>
+  </si>
+  <si>
+    <t>フェンシング体験</t>
+  </si>
+  <si>
+    <t>自動車部活動紹介</t>
+  </si>
+  <si>
+    <t>ラグビー部活動紹介</t>
+  </si>
+  <si>
+    <t>仮タイトル</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">カリタイトル </t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>アニメ制作って実際何するの？</t>
+    <phoneticPr fontId="5"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1136,14 +1210,6 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1165,7 +1231,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1173,12 +1239,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF5B3F86"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1191,7 +1266,6 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1208,6 +1282,20 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1538,13 +1626,14 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="47" customWidth="1"/>
-    <col min="4" max="4" width="14.5" customWidth="1"/>
-    <col min="5" max="6" width="10.83203125" customWidth="1"/>
-    <col min="7" max="7" width="30.33203125" customWidth="1"/>
-    <col min="8" max="8" width="36.33203125" customWidth="1"/>
-    <col min="9" max="9" width="26.6640625" customWidth="1"/>
-    <col min="10" max="10" width="32.6640625" customWidth="1"/>
+    <col min="3" max="3" width="47" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5" hidden="1" customWidth="1"/>
+    <col min="5" max="6" width="10.83203125" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="30.33203125" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="36.33203125" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="26.6640625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="32.6640625" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="26.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -1581,6 +1670,15 @@
       <c r="K1" s="3" t="s">
         <v>214</v>
       </c>
+      <c r="L1" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>278</v>
+      </c>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2">
@@ -1592,27 +1690,35 @@
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11" t="s">
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10" t="s">
         <v>5</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="1"/>
+      <c r="L2" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>228</v>
+      </c>
     </row>
     <row r="3" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3">
@@ -1624,31 +1730,32 @@
       <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="K3" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="N3" s="2"/>
+      <c r="L3" s="16"/>
+      <c r="N3" s="12"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4">
@@ -1660,31 +1767,39 @@
       <c r="C4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="10" t="s">
         <v>18</v>
       </c>
       <c r="K4" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="N4" s="6"/>
+      <c r="L4" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="M4">
+        <v>11</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>234</v>
+      </c>
     </row>
     <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5">
@@ -1696,27 +1811,36 @@
       <c r="C5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="H5" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11" t="s">
+      <c r="I5" s="10"/>
+      <c r="J5" s="10" t="s">
         <v>25</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>6</v>
+      </c>
+      <c r="L5" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="M5">
+        <v>7</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -1729,28 +1853,30 @@
       <c r="C6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="J6" s="11"/>
+      <c r="J6" s="10"/>
       <c r="K6" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="L6" s="15"/>
+      <c r="N6" s="13"/>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7">
@@ -1762,27 +1888,36 @@
       <c r="C7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="H7" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11" t="s">
+      <c r="I7" s="10"/>
+      <c r="J7" s="10" t="s">
         <v>34</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>229</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>281</v>
+      </c>
+      <c r="M7">
+        <v>8</v>
+      </c>
+      <c r="N7" s="14" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -1795,27 +1930,36 @@
       <c r="C8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="H8" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11" t="s">
+      <c r="I8" s="10"/>
+      <c r="J8" s="10" t="s">
         <v>39</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>6</v>
+      </c>
+      <c r="L8" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="M8">
+        <v>7</v>
+      </c>
+      <c r="N8" s="14" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -1828,29 +1972,38 @@
       <c r="C9" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="H9" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="J9" s="11" t="s">
+      <c r="J9" s="10" t="s">
         <v>47</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>232</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="M9">
+        <v>10</v>
+      </c>
+      <c r="N9" s="7" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -1863,25 +2016,34 @@
       <c r="C10" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="H10" s="11" t="s">
+      <c r="H10" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
       <c r="K10" s="1" t="s">
         <v>6</v>
+      </c>
+      <c r="L10" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="M10">
+        <v>16</v>
+      </c>
+      <c r="N10" s="14" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -1894,25 +2056,34 @@
       <c r="C11" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="G11" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11" t="s">
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10" t="s">
         <v>57</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>6</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>284</v>
+      </c>
+      <c r="M11">
+        <v>18</v>
+      </c>
+      <c r="N11" s="7" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -1925,27 +2096,36 @@
       <c r="C12" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="G12" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="H12" s="11" t="s">
+      <c r="H12" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11" t="s">
+      <c r="I12" s="10"/>
+      <c r="J12" s="10" t="s">
         <v>64</v>
       </c>
       <c r="K12" s="5" t="s">
         <v>232</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="M12">
+        <v>6</v>
+      </c>
+      <c r="N12" s="14" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -1958,27 +2138,36 @@
       <c r="C13" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="H13" s="11" t="s">
+      <c r="H13" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11" t="s">
+      <c r="I13" s="10"/>
+      <c r="J13" s="10" t="s">
         <v>71</v>
       </c>
       <c r="K13" s="5" t="s">
         <v>230</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="M13">
+        <v>17</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -1991,29 +2180,38 @@
       <c r="C14" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="G14" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="H14" s="11" t="s">
+      <c r="H14" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="I14" s="11" t="s">
+      <c r="I14" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="J14" s="11" t="s">
+      <c r="J14" s="10" t="s">
         <v>79</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>6</v>
+      </c>
+      <c r="L14" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="M14">
+        <v>2</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -2026,30 +2224,32 @@
       <c r="C15" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F15" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="G15" s="11" t="s">
+      <c r="G15" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="H15" s="11" t="s">
+      <c r="H15" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="I15" s="11" t="s">
+      <c r="I15" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="J15" s="11" t="s">
+      <c r="J15" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="K15" s="10" t="s">
+      <c r="K15" s="9" t="s">
         <v>267</v>
       </c>
+      <c r="L15" s="16"/>
+      <c r="N15" s="13"/>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16">
@@ -2061,28 +2261,37 @@
       <c r="C16" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="F16" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="G16" s="12" t="s">
+      <c r="G16" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="H16" s="11" t="s">
+      <c r="H16" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
       <c r="K16" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L16" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="M16">
+        <v>16</v>
+      </c>
+      <c r="N16" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2092,30 +2301,39 @@
       <c r="C17" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="F17" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="G17" s="11" t="s">
+      <c r="G17" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="H17" s="11" t="s">
+      <c r="H17" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11" t="s">
+      <c r="I17" s="10"/>
+      <c r="J17" s="10" t="s">
         <v>97</v>
       </c>
       <c r="K17" s="5" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L17" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17" s="14" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2125,32 +2343,34 @@
       <c r="C18" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="E18" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="F18" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="G18" s="11" t="s">
+      <c r="G18" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="H18" s="11" t="s">
+      <c r="H18" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="I18" s="11" t="s">
+      <c r="I18" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="J18" s="11" t="s">
+      <c r="J18" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="K18" s="9" t="s">
+      <c r="K18" s="8" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L18" s="15"/>
+      <c r="N18" s="13"/>
+    </row>
+    <row r="19" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2160,30 +2380,39 @@
       <c r="C19" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="E19" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="F19" s="11" t="s">
+      <c r="F19" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="G19" s="11" t="s">
+      <c r="G19" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="H19" s="11" t="s">
+      <c r="H19" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11" t="s">
+      <c r="I19" s="10"/>
+      <c r="J19" s="10" t="s">
         <v>112</v>
       </c>
       <c r="K19" s="5" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L19" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="M19">
+        <v>5</v>
+      </c>
+      <c r="N19" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2193,30 +2422,39 @@
       <c r="C20" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="E20" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="F20" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="G20" s="11" t="s">
+      <c r="G20" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="H20" s="11" t="s">
+      <c r="H20" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11" t="s">
+      <c r="I20" s="10"/>
+      <c r="J20" s="10" t="s">
         <v>118</v>
       </c>
       <c r="K20" s="5" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L20" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="M20">
+        <v>8</v>
+      </c>
+      <c r="N20" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2226,32 +2464,41 @@
       <c r="C21" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="E21" s="11" t="s">
+      <c r="E21" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="F21" s="11" t="s">
+      <c r="F21" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="G21" s="12" t="s">
+      <c r="G21" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="H21" s="12" t="s">
+      <c r="H21" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="I21" s="11" t="s">
+      <c r="I21" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="J21" s="11" t="s">
+      <c r="J21" s="10" t="s">
         <v>124</v>
       </c>
       <c r="K21" s="5" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L21" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="M21">
+        <v>4</v>
+      </c>
+      <c r="N21" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2261,32 +2508,41 @@
       <c r="C22" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="E22" s="11" t="s">
+      <c r="E22" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="F22" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="G22" s="11" t="s">
+      <c r="G22" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="H22" s="11" t="s">
+      <c r="H22" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="I22" s="11" t="s">
+      <c r="I22" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="J22" s="11" t="s">
+      <c r="J22" s="10" t="s">
         <v>132</v>
       </c>
       <c r="K22" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L22" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="M22">
+        <v>19</v>
+      </c>
+      <c r="N22" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2296,30 +2552,39 @@
       <c r="C23" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="E23" s="11" t="s">
+      <c r="E23" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="F23" s="11" t="s">
+      <c r="F23" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="G23" s="11" t="s">
+      <c r="G23" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="H23" s="11" t="s">
+      <c r="H23" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="I23" s="11"/>
-      <c r="J23" s="11" t="s">
+      <c r="I23" s="10"/>
+      <c r="J23" s="10" t="s">
         <v>138</v>
       </c>
       <c r="K23" s="5" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L23" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="M23">
+        <v>14</v>
+      </c>
+      <c r="N23" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2329,32 +2594,34 @@
       <c r="C24" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="E24" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="F24" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="G24" s="11" t="s">
+      <c r="G24" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="H24" s="11" t="s">
+      <c r="H24" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="I24" s="11" t="s">
+      <c r="I24" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="J24" s="11" t="s">
+      <c r="J24" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="K24" s="9" t="s">
+      <c r="K24" s="8" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L24" s="16"/>
+      <c r="N24" s="13"/>
+    </row>
+    <row r="25" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2364,28 +2631,37 @@
       <c r="C25" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="E25" s="11" t="s">
+      <c r="E25" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="F25" s="11" t="s">
+      <c r="F25" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="G25" s="11" t="s">
+      <c r="G25" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11" t="s">
+      <c r="H25" s="10"/>
+      <c r="I25" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="J25" s="11"/>
+      <c r="J25" s="10"/>
       <c r="K25" s="5" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L25" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="M25">
+        <v>9</v>
+      </c>
+      <c r="N25" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2395,30 +2671,39 @@
       <c r="C26" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="D26" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="E26" s="11" t="s">
+      <c r="E26" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="F26" s="11" t="s">
+      <c r="F26" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="G26" s="11" t="s">
+      <c r="G26" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="H26" s="11" t="s">
+      <c r="H26" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="I26" s="11"/>
-      <c r="J26" s="11" t="s">
+      <c r="I26" s="10"/>
+      <c r="J26" s="10" t="s">
         <v>155</v>
       </c>
       <c r="K26" s="5" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L26" s="16" t="s">
+        <v>289</v>
+      </c>
+      <c r="M26">
+        <v>13</v>
+      </c>
+      <c r="N26" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2428,30 +2713,39 @@
       <c r="C27" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="D27" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="E27" s="11" t="s">
+      <c r="E27" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="F27" s="11" t="s">
+      <c r="F27" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="G27" s="11" t="s">
+      <c r="G27" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="H27" s="11" t="s">
+      <c r="H27" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="I27" s="11"/>
-      <c r="J27" s="11" t="s">
+      <c r="I27" s="10"/>
+      <c r="J27" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="K27" s="7" t="s">
+      <c r="K27" s="6" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L27" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="M27">
+        <v>19</v>
+      </c>
+      <c r="N27" s="14" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2461,28 +2755,37 @@
       <c r="C28" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="D28" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="E28" s="11" t="s">
+      <c r="E28" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="F28" s="11" t="s">
+      <c r="F28" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="G28" s="11" t="s">
+      <c r="G28" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="H28" s="11"/>
-      <c r="I28" s="11"/>
-      <c r="J28" s="11" t="s">
+      <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10" t="s">
         <v>166</v>
       </c>
       <c r="K28" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L28" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="M28">
+        <v>14</v>
+      </c>
+      <c r="N28" s="14" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2492,32 +2795,41 @@
       <c r="C29" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="D29" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="E29" s="11" t="s">
+      <c r="E29" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="F29" s="11" t="s">
+      <c r="F29" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="G29" s="11" t="s">
+      <c r="G29" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="H29" s="11" t="s">
+      <c r="H29" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="I29" s="11" t="s">
+      <c r="I29" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="J29" s="11" t="s">
+      <c r="J29" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="K29" s="7" t="s">
+      <c r="K29" s="6" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L29" s="15" t="s">
+        <v>291</v>
+      </c>
+      <c r="M29">
+        <v>2</v>
+      </c>
+      <c r="N29" s="14" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2527,30 +2839,39 @@
       <c r="C30" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="D30" s="8" t="s">
+      <c r="D30" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="E30" s="11" t="s">
+      <c r="E30" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="F30" s="11" t="s">
+      <c r="F30" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="G30" s="11" t="s">
+      <c r="G30" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="H30" s="11" t="s">
+      <c r="H30" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="I30" s="11"/>
-      <c r="J30" s="11" t="s">
+      <c r="I30" s="10"/>
+      <c r="J30" s="10" t="s">
         <v>180</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L30" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="M30">
+        <v>9</v>
+      </c>
+      <c r="N30" s="14" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2560,26 +2881,35 @@
       <c r="C31" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="D31" s="8" t="s">
+      <c r="D31" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="E31" s="11" t="s">
+      <c r="E31" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="F31" s="11" t="s">
+      <c r="F31" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="G31" s="11" t="s">
+      <c r="G31" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="H31" s="11"/>
-      <c r="I31" s="11"/>
-      <c r="J31" s="11"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="10"/>
+      <c r="J31" s="10"/>
       <c r="K31" s="5" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L31" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="M31">
+        <v>10</v>
+      </c>
+      <c r="N31" s="14" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2589,28 +2919,37 @@
       <c r="C32" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D32" s="8" t="s">
+      <c r="D32" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="E32" s="11" t="s">
+      <c r="E32" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="F32" s="11" t="s">
+      <c r="F32" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="G32" s="11" t="s">
+      <c r="G32" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="H32" s="11" t="s">
+      <c r="H32" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="I32" s="11"/>
-      <c r="J32" s="11"/>
+      <c r="I32" s="10"/>
+      <c r="J32" s="10"/>
       <c r="K32" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L32" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="M32">
+        <v>6</v>
+      </c>
+      <c r="N32" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2620,28 +2959,37 @@
       <c r="C33" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="D33" s="8" t="s">
+      <c r="D33" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="E33" s="11" t="s">
+      <c r="E33" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="F33" s="11" t="s">
+      <c r="F33" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="G33" s="11" t="s">
+      <c r="G33" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="H33" s="11"/>
-      <c r="I33" s="11"/>
-      <c r="J33" s="11" t="s">
+      <c r="H33" s="10"/>
+      <c r="I33" s="10"/>
+      <c r="J33" s="10" t="s">
         <v>194</v>
       </c>
       <c r="K33" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L33" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="M33">
+        <v>17</v>
+      </c>
+      <c r="N33" s="14" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2651,26 +2999,35 @@
       <c r="C34" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="D34" s="8" t="s">
+      <c r="D34" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="E34" s="11" t="s">
+      <c r="E34" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="11" t="s">
+      <c r="F34" s="10"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="I34" s="11"/>
-      <c r="J34" s="11" t="s">
+      <c r="I34" s="10"/>
+      <c r="J34" s="10" t="s">
         <v>198</v>
       </c>
       <c r="K34" s="5" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L34" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="M34">
+        <v>15</v>
+      </c>
+      <c r="N34" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2680,22 +3037,24 @@
       <c r="C35" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D35" s="8" t="s">
+      <c r="D35" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="E35" s="11" t="s">
+      <c r="E35" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="11"/>
-      <c r="J35" s="11"/>
-      <c r="K35" s="9" t="s">
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="10"/>
+      <c r="I35" s="10"/>
+      <c r="J35" s="10"/>
+      <c r="K35" s="8" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L35" s="15"/>
+      <c r="N35" s="13"/>
+    </row>
+    <row r="36" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2705,30 +3064,39 @@
       <c r="C36" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="D36" s="8" t="s">
+      <c r="D36" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="E36" s="11" t="s">
+      <c r="E36" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="F36" s="11" t="s">
+      <c r="F36" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="G36" s="11" t="s">
+      <c r="G36" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="H36" s="11" t="s">
+      <c r="H36" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="I36" s="11"/>
-      <c r="J36" s="11" t="s">
+      <c r="I36" s="10"/>
+      <c r="J36" s="10" t="s">
         <v>205</v>
       </c>
       <c r="K36" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L36" s="17" t="s">
+        <v>295</v>
+      </c>
+      <c r="M36">
+        <v>3</v>
+      </c>
+      <c r="N36" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2738,26 +3106,35 @@
       <c r="C37" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="D37" s="8" t="s">
+      <c r="D37" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="E37" s="12" t="s">
+      <c r="E37" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11" t="s">
+      <c r="F37" s="10"/>
+      <c r="G37" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="H37" s="11" t="s">
+      <c r="H37" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="I37" s="11"/>
-      <c r="J37" s="11"/>
+      <c r="I37" s="10"/>
+      <c r="J37" s="10"/>
       <c r="K37" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L37" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="M37">
+        <v>13</v>
+      </c>
+      <c r="N37" s="14" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2767,27 +3144,36 @@
       <c r="C38" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="D38" s="8" t="s">
+      <c r="D38" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="E38" s="12" t="s">
+      <c r="E38" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="F38" s="11" t="s">
+      <c r="F38" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="G38" s="11" t="s">
+      <c r="G38" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="H38" s="11" t="s">
+      <c r="H38" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="I38" s="11"/>
-      <c r="J38" s="11" t="s">
+      <c r="I38" s="10"/>
+      <c r="J38" s="10" t="s">
         <v>224</v>
       </c>
       <c r="K38" s="1" t="s">
         <v>6</v>
+      </c>
+      <c r="L38" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="M38">
+        <v>12</v>
+      </c>
+      <c r="N38" s="7" t="s">
+        <v>234</v>
       </c>
     </row>
   </sheetData>

--- a/data/wakabasai_exhibitor.xlsx
+++ b/data/wakabasai_exhibitor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/haru/Documents/webdev/wakabasai2026/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5A8D5C8-8FCB-A148-9681-D869712D451A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AA12C80-8AE9-E641-BAED-030E1469AFBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="580" windowWidth="25600" windowHeight="16060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="309">
   <si>
     <t>ロボット技術研究会</t>
   </si>
@@ -1130,14 +1130,67 @@
     <t>ラグビー部活動紹介</t>
   </si>
   <si>
-    <t>仮タイトル</t>
-    <rPh sb="0" eb="1">
-      <t xml:space="preserve">カリタイトル </t>
+    <t>アニメ制作って実際何するの？</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>traPの活動紹介</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>グライダー部の活動紹介</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>管弦楽団の活動紹介</t>
+    <rPh sb="0" eb="4">
+      <t xml:space="preserve">カンゲンガクダン </t>
     </rPh>
     <phoneticPr fontId="5"/>
   </si>
   <si>
-    <t>アニメ制作って実際何するの？</t>
+    <t>デザイン研究会の活動紹介</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>ScienceTechnoの活動紹介</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>コール・クライネスの活動紹介</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>合氣道部の活動紹介</t>
+    <rPh sb="0" eb="4">
+      <t>アイキドウブ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>レゴ同好会の活動紹介</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>アメフトの活動紹介</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>お笑いサークルオゾンの活動紹介</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>TPGの活動紹介</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>漕艇部の活動紹介</t>
+    <rPh sb="0" eb="3">
+      <t xml:space="preserve">ソウテイブ </t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t xml:space="preserve">カツドウショウカイ </t>
+    </rPh>
     <phoneticPr fontId="5"/>
   </si>
 </sst>
@@ -1792,7 +1845,7 @@
         <v>274</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="M4">
         <v>11</v>
@@ -1997,7 +2050,7 @@
         <v>232</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M9">
         <v>10</v>
@@ -2119,7 +2172,7 @@
         <v>232</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="M12">
         <v>6</v>
@@ -2161,7 +2214,7 @@
         <v>230</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="M13">
         <v>17</v>
@@ -2324,7 +2377,7 @@
         <v>232</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="M17">
         <v>1</v>
@@ -2403,7 +2456,7 @@
         <v>233</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="M19">
         <v>5</v>
@@ -2489,7 +2542,7 @@
         <v>230</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="M21">
         <v>4</v>
@@ -2575,7 +2628,7 @@
         <v>230</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="M23">
         <v>14</v>
@@ -2652,7 +2705,7 @@
         <v>232</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="M25">
         <v>9</v>
@@ -2900,7 +2953,7 @@
         <v>232</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="M31">
         <v>10</v>
@@ -3018,7 +3071,7 @@
         <v>229</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="M34">
         <v>15</v>
@@ -3125,7 +3178,7 @@
         <v>6</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="M37">
         <v>13</v>
@@ -3167,7 +3220,7 @@
         <v>6</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="M38">
         <v>12</v>
